--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4637DB68-05F5-47F6-B64D-8A9CD0B9BDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E9D17-A7AD-4F4D-A376-E0B81BD267F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -674,7 +674,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -718,7 +717,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -741,7 +740,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -764,7 +763,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -787,7 +786,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -810,7 +809,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -836,7 +835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -862,7 +861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -888,7 +887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -914,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1145,7 +1144,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1168,7 +1167,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1191,7 +1190,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1214,7 +1213,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1237,7 +1236,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1260,7 +1259,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1283,7 +1282,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1306,7 +1305,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1329,7 +1328,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1352,7 +1351,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1398,7 +1397,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1421,7 +1420,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1444,7 +1443,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1467,7 +1466,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1490,7 +1489,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1513,7 +1512,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1535,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1582,7 +1581,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1605,7 +1604,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1628,7 +1627,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1651,7 +1650,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1674,7 +1673,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1720,7 +1719,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1743,7 +1742,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1789,7 +1788,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1812,7 +1811,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1858,7 +1857,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1881,7 +1880,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1904,7 +1903,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1927,7 +1926,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1950,7 +1949,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1973,7 +1972,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -1996,7 +1995,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2019,7 +2018,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2065,7 +2064,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2088,7 +2087,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2111,7 +2110,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2157,7 +2156,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2226,7 +2225,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2249,7 +2248,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2321,7 +2320,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2344,7 +2343,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2367,7 +2366,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2436,7 +2435,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2450,7 +2449,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2473,7 +2472,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2496,7 +2495,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2519,7 +2518,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2542,7 +2541,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2611,7 +2610,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2634,7 +2633,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2717,7 +2716,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2737,7 +2736,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2777,7 +2776,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2869,7 +2868,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2895,7 +2894,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2918,7 +2917,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2941,7 +2940,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3056,7 +3055,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3079,7 +3078,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3125,7 +3124,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3148,7 +3147,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3171,7 +3170,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3217,7 +3216,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3240,7 +3239,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3292,7 +3291,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3315,7 +3314,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3332,7 +3331,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3355,7 +3354,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3378,7 +3377,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3401,7 +3400,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3424,7 +3423,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3447,7 +3446,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3493,7 +3492,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3516,7 +3515,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3539,7 +3538,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3562,7 +3561,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3588,7 +3587,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3634,7 +3633,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3657,7 +3656,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3680,7 +3679,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3703,7 +3702,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3726,7 +3725,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3775,7 +3774,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3821,7 +3820,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3844,7 +3843,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3867,7 +3866,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3922,7 +3921,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -3971,7 +3970,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4020,7 +4019,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4046,7 +4045,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4072,7 +4071,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4141,7 +4140,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4196,7 +4195,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4222,7 +4221,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4248,7 +4247,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4271,7 +4270,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4320,7 +4319,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4346,7 +4345,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4372,7 +4371,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4398,7 +4397,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4424,7 +4423,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4450,7 +4449,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4476,7 +4475,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4502,7 +4501,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4528,7 +4527,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4583,7 +4582,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4609,7 +4608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4658,7 +4657,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4681,7 +4680,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4707,7 +4706,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4730,7 +4729,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4785,7 +4784,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4811,7 +4810,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -4840,7 +4839,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4854,7 +4853,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4868,7 +4867,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4882,7 +4881,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4896,7 +4895,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4910,7 +4909,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4938,7 +4937,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4952,7 +4951,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4966,7 +4965,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4980,7 +4979,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -4994,7 +4993,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5008,7 +5007,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5036,7 +5035,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5050,7 +5049,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5064,7 +5063,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5078,7 +5077,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5106,7 +5105,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5120,7 +5119,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5186,7 +5185,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5232,7 +5231,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5258,7 +5257,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5278,7 +5277,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5307,7 +5306,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5362,7 +5361,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5408,7 +5407,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5428,7 +5427,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5480,7 +5479,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5509,7 +5508,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5527,6 +5526,9 @@
       </c>
       <c r="F212" s="1">
         <v>46056</v>
+      </c>
+      <c r="G212" s="1">
+        <v>46066</v>
       </c>
       <c r="I212">
         <v>15490</v>
@@ -5555,7 +5557,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5578,7 +5580,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5601,7 +5603,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5624,7 +5626,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5647,7 +5649,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5670,7 +5672,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5694,13 +5696,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A219" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="028/2023"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:A219" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E9D17-A7AD-4F4D-A376-E0B81BD267F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECC466E-9FB1-4DF0-A79A-0AB461BBD5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$220</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="95">
   <si>
     <t>007/2024</t>
   </si>
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I219"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5695,8 +5695,22 @@
         <v>46048</v>
       </c>
     </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1</v>
+      </c>
+      <c r="B220">
+        <v>21</v>
+      </c>
+      <c r="C220" s="1">
+        <v>46076</v>
+      </c>
+      <c r="D220" s="2">
+        <v>23842.17</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A219" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A220" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECC466E-9FB1-4DF0-A79A-0AB461BBD5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDDC9D7-04F5-4F81-9E74-AE3FE61461BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -5553,6 +5553,9 @@
       <c r="F213" s="1">
         <v>46062</v>
       </c>
+      <c r="G213" s="1">
+        <v>46073</v>
+      </c>
       <c r="I213">
         <v>15606</v>
       </c>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDDC9D7-04F5-4F81-9E74-AE3FE61461BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BAA210-9AD2-453A-9C23-EA32BF8B6DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -5711,6 +5711,15 @@
       <c r="D220" s="2">
         <v>23842.17</v>
       </c>
+      <c r="E220">
+        <v>337</v>
+      </c>
+      <c r="F220" s="1">
+        <v>46079</v>
+      </c>
+      <c r="I220">
+        <v>15798</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A220" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BAA210-9AD2-453A-9C23-EA32BF8B6DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE17CA0E-1D34-4071-BB61-5934E259F4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$222</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="97">
   <si>
     <t>007/2024</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>os  = 4.243,08m²/med=3.970,31m²</t>
+  </si>
+  <si>
+    <t>9 do 4</t>
+  </si>
+  <si>
+    <t>os = 3.403,50m²/med=3.151,21m²</t>
   </si>
 </sst>
 </file>
@@ -674,7 +680,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I220"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -717,7 +724,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -740,7 +747,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -763,7 +770,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -786,7 +793,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -809,7 +816,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -835,7 +842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -861,7 +868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -887,7 +894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -913,7 +920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1144,7 +1151,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1167,7 +1174,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1190,7 +1197,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1213,7 +1220,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1236,7 +1243,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1259,7 +1266,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1282,7 +1289,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1305,7 +1312,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1335,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1351,7 +1358,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1374,7 +1381,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1397,7 +1404,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1420,7 +1427,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1443,7 +1450,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1466,7 +1473,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1489,7 +1496,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1512,7 +1519,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1542,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1565,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1581,7 +1588,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1604,7 +1611,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1627,7 +1634,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1650,7 +1657,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1673,7 +1680,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1696,7 +1703,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1719,7 +1726,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1742,7 +1749,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1765,7 +1772,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1788,7 +1795,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1811,7 +1818,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1834,7 +1841,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1857,7 +1864,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1880,7 +1887,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1903,7 +1910,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1926,7 +1933,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1949,7 +1956,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1972,7 +1979,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -1995,7 +2002,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2018,7 +2025,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +2048,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2064,7 +2071,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2087,7 +2094,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2110,7 +2117,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2133,7 +2140,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2156,7 +2163,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2179,7 +2186,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2202,7 +2209,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2225,7 +2232,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2248,7 +2255,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2297,7 +2304,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2320,7 +2327,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2343,7 +2350,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2366,7 +2373,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2389,7 +2396,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2412,7 +2419,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2435,7 +2442,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2449,7 +2456,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2472,7 +2479,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +2502,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2518,7 +2525,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2541,7 +2548,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2564,7 +2571,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2587,7 +2594,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2610,7 +2617,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2633,7 +2640,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2656,7 +2663,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -2676,7 +2683,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2696,7 +2703,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2716,7 +2723,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2736,7 +2743,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2756,7 +2763,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2776,7 +2783,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2796,7 +2803,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2816,7 +2823,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2842,7 +2849,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2868,7 +2875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2894,7 +2901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2917,7 +2924,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2940,7 +2947,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2963,7 +2970,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -2986,7 +2993,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3009,7 +3016,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3032,7 +3039,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3055,7 +3062,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3078,7 +3085,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3101,7 +3108,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3124,7 +3131,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3147,7 +3154,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3170,7 +3177,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3193,7 +3200,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3216,7 +3223,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3239,7 +3246,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3291,7 +3298,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3314,7 +3321,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3331,7 +3338,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3354,7 +3361,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3377,7 +3384,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3400,7 +3407,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3423,7 +3430,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3446,7 +3453,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3469,7 +3476,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3492,7 +3499,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3515,7 +3522,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3538,7 +3545,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3561,7 +3568,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3587,7 +3594,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3610,7 +3617,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3633,7 +3640,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3656,7 +3663,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3679,7 +3686,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3702,7 +3709,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3725,7 +3732,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3774,7 +3781,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3797,7 +3804,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3820,7 +3827,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3843,7 +3850,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3866,7 +3873,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3921,7 +3928,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3944,7 +3951,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -3970,7 +3977,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -3996,7 +4003,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4019,7 +4026,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4045,7 +4052,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4071,7 +4078,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4094,7 +4101,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4120,7 +4127,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4140,7 +4147,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4195,7 +4202,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4221,7 +4228,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4247,7 +4254,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4270,7 +4277,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4293,7 +4300,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4319,7 +4326,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4345,7 +4352,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4371,7 +4378,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4397,7 +4404,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4423,7 +4430,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4449,7 +4456,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4475,7 +4482,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4501,7 +4508,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4527,7 +4534,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4582,7 +4589,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4608,7 +4615,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4657,7 +4664,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4680,7 +4687,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4706,7 +4713,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4729,7 +4736,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4784,7 +4791,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4810,7 +4817,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -4839,7 +4846,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4853,7 +4860,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4867,7 +4874,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4881,7 +4888,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4895,7 +4902,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4909,7 +4916,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4923,7 +4930,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4937,7 +4944,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4951,7 +4958,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4965,7 +4972,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4979,7 +4986,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -4993,7 +5000,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5007,7 +5014,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5021,7 +5028,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5035,7 +5042,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5049,7 +5056,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5063,7 +5070,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5077,7 +5084,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5091,7 +5098,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5105,7 +5112,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5119,7 +5126,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5171,7 +5178,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5185,7 +5192,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5208,7 +5215,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5231,7 +5238,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5257,7 +5264,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5277,7 +5284,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5306,7 +5313,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5335,7 +5342,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5361,7 +5368,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5407,7 +5414,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5427,7 +5434,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5479,7 +5486,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5508,7 +5515,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5560,7 +5567,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5583,7 +5590,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5606,7 +5613,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5629,7 +5636,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5652,7 +5659,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5675,7 +5682,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5721,8 +5728,71 @@
         <v>15798</v>
       </c>
     </row>
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>5</v>
+      </c>
+      <c r="B221" t="s">
+        <v>95</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46080</v>
+      </c>
+      <c r="D221" s="2">
+        <v>734795.99</v>
+      </c>
+      <c r="E221">
+        <v>1131</v>
+      </c>
+      <c r="F221" s="1">
+        <v>46084</v>
+      </c>
+      <c r="H221" t="s">
+        <v>96</v>
+      </c>
+      <c r="I221">
+        <v>15869</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>0</v>
+      </c>
+      <c r="B222">
+        <v>18</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46085</v>
+      </c>
+      <c r="D222" s="2">
+        <v>170056.62</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>1</v>
+      </c>
+      <c r="B223">
+        <v>22</v>
+      </c>
+      <c r="C223" s="1">
+        <v>46086</v>
+      </c>
+      <c r="D223" s="2">
+        <v>65166.97</v>
+      </c>
+      <c r="I223">
+        <v>15927</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A220" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A222" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="028/2023"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE17CA0E-1D34-4071-BB61-5934E259F4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E45834-1453-45B4-8100-D216C5FFC8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -5724,6 +5724,9 @@
       <c r="F220" s="1">
         <v>46079</v>
       </c>
+      <c r="G220" s="1">
+        <v>46086</v>
+      </c>
       <c r="I220">
         <v>15798</v>
       </c>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E45834-1453-45B4-8100-D216C5FFC8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF91ACDF-8E99-4321-B7D5-7D65F4BC43CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$223</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -816,7 +816,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -842,7 +842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -868,7 +868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -894,7 +894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -920,7 +920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -946,7 +946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -972,7 +972,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -998,7 +998,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5749,6 +5749,9 @@
       </c>
       <c r="F221" s="1">
         <v>46084</v>
+      </c>
+      <c r="G221" s="1">
+        <v>46087</v>
       </c>
       <c r="H221" t="s">
         <v>96</v>
@@ -5771,7 +5774,7 @@
         <v>170056.62</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5789,10 +5792,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A222" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:A223" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="028/2023"/>
+        <filter val="009/2022"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF91ACDF-8E99-4321-B7D5-7D65F4BC43CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A894598A-2F6E-4384-BA13-D22DD7C7BED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -680,7 +680,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -724,7 +723,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -747,7 +746,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -770,7 +769,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -793,7 +792,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -946,7 +945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -972,7 +971,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -998,7 +997,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1024,7 +1023,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1050,7 +1049,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1076,7 +1075,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1102,7 +1101,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1128,7 +1127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1174,7 +1173,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1243,7 +1242,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1266,7 +1265,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1289,7 +1288,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1335,7 +1334,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1358,7 +1357,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1381,7 +1380,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1404,7 +1403,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1427,7 +1426,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1473,7 +1472,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1496,7 +1495,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1519,7 +1518,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1541,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1564,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1588,7 +1587,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1611,7 +1610,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1634,7 +1633,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1680,7 +1679,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1726,7 +1725,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1772,7 +1771,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1795,7 +1794,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1910,7 +1909,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1956,7 +1955,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1979,7 +1978,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2002,7 +2001,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2025,7 +2024,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2094,7 +2093,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2140,7 +2139,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2163,7 +2162,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2209,7 +2208,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2255,7 +2254,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2278,7 +2277,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2304,7 +2303,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2327,7 +2326,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2350,7 +2349,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2442,7 +2441,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2456,7 +2455,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2571,7 +2570,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2594,7 +2593,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2617,7 +2616,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2640,7 +2639,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2683,7 +2682,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2723,7 +2722,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2743,7 +2742,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2763,7 +2762,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2823,7 +2822,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2849,7 +2848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2970,7 +2969,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -2993,7 +2992,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3016,7 +3015,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3039,7 +3038,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3085,7 +3084,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3108,7 +3107,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3154,7 +3153,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3177,7 +3176,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3223,7 +3222,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3246,7 +3245,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3269,7 +3268,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3361,7 +3360,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3384,7 +3383,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3430,7 +3429,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3453,7 +3452,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3476,7 +3475,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3499,7 +3498,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3522,7 +3521,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3545,7 +3544,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3568,7 +3567,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3617,7 +3616,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3640,7 +3639,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3663,7 +3662,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3709,7 +3708,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3732,7 +3731,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3755,7 +3754,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3781,7 +3780,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3804,7 +3803,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3850,7 +3849,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3899,7 +3898,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -3928,7 +3927,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -3977,7 +3976,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4026,7 +4025,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4052,7 +4051,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4127,7 +4126,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4147,7 +4146,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4173,7 +4172,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4202,7 +4201,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4254,7 +4253,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4277,7 +4276,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4326,7 +4325,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4378,7 +4377,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4404,7 +4403,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4430,7 +4429,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4456,7 +4455,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4482,7 +4481,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4508,7 +4507,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4534,7 +4533,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4560,7 +4559,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4589,7 +4588,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4615,7 +4614,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4638,7 +4637,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4664,7 +4663,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4713,7 +4712,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4736,7 +4735,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4765,7 +4764,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4791,7 +4790,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4846,7 +4845,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4888,7 +4887,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4902,7 +4901,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4916,7 +4915,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4930,7 +4929,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4944,7 +4943,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4958,7 +4957,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4972,7 +4971,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4986,7 +4985,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -5000,7 +4999,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5014,7 +5013,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5028,7 +5027,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5042,7 +5041,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5056,7 +5055,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5070,7 +5069,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5084,7 +5083,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5098,7 +5097,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5112,7 +5111,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5126,7 +5125,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5152,7 +5151,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5178,7 +5177,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5192,7 +5191,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5215,7 +5214,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5238,7 +5237,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5264,7 +5263,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5284,7 +5283,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5342,7 +5341,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5368,7 +5367,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5391,7 +5390,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5414,7 +5413,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5434,7 +5433,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5460,7 +5459,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5515,7 +5514,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5541,7 +5540,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5590,7 +5589,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5613,7 +5612,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5636,7 +5635,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5659,7 +5658,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5682,7 +5681,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5705,7 +5704,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5760,7 +5759,7 @@
         <v>15869</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -5773,8 +5772,14 @@
       <c r="D222" s="2">
         <v>170056.62</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E222">
+        <v>300</v>
+      </c>
+      <c r="F222" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5787,18 +5792,21 @@
       <c r="D223" s="2">
         <v>65166.97</v>
       </c>
+      <c r="E223">
+        <v>338</v>
+      </c>
+      <c r="F223" s="1">
+        <v>46094</v>
+      </c>
+      <c r="G223" s="1">
+        <v>46094</v>
+      </c>
       <c r="I223">
         <v>15927</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A223" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="009/2022"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:A223" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A894598A-2F6E-4384-BA13-D22DD7C7BED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8AE36F-0411-4679-9F3D-52FE86358C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$224</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="99">
   <si>
     <t>007/2024</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>os = 3.403,50m²/med=3.151,21m²</t>
+  </si>
+  <si>
+    <t>10 do 4</t>
+  </si>
+  <si>
+    <t>os = 3.127,65m²/med=2.860,85m²</t>
   </si>
 </sst>
 </file>
@@ -680,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:I224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5805,8 +5811,28 @@
         <v>15927</v>
       </c>
     </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>5</v>
+      </c>
+      <c r="B224" t="s">
+        <v>97</v>
+      </c>
+      <c r="C224" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D224" s="2">
+        <v>667090.13</v>
+      </c>
+      <c r="H224" t="s">
+        <v>98</v>
+      </c>
+      <c r="I224">
+        <v>16175</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A223" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A224" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8AE36F-0411-4679-9F3D-52FE86358C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF332D5-6BB0-4D86-B842-BA67CE18F9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -5824,6 +5824,12 @@
       <c r="D224" s="2">
         <v>667090.13</v>
       </c>
+      <c r="E224">
+        <v>1142</v>
+      </c>
+      <c r="F224" s="1">
+        <v>46113</v>
+      </c>
       <c r="H224" t="s">
         <v>98</v>
       </c>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF332D5-6BB0-4D86-B842-BA67CE18F9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D185F7-B97E-4DBC-A609-2E65AA8A9E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -739,7 +739,7 @@
       <c r="C2" s="1">
         <v>45483</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>117383.14</v>
       </c>
       <c r="E2">

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D185F7-B97E-4DBC-A609-2E65AA8A9E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3D394-BFCB-4D5D-B16E-246882656FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$225</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="99">
   <si>
     <t>007/2024</t>
   </si>
@@ -686,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I224"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5837,8 +5837,25 @@
         <v>16175</v>
       </c>
     </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>1</v>
+      </c>
+      <c r="B225">
+        <v>23</v>
+      </c>
+      <c r="C225" s="1">
+        <v>46112</v>
+      </c>
+      <c r="D225" s="2">
+        <v>42382.32</v>
+      </c>
+      <c r="I225">
+        <v>16187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A224" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A225" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3D394-BFCB-4D5D-B16E-246882656FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5362056C-41FF-49E3-BD13-988B873EEC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$226</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="99">
   <si>
     <t>007/2024</t>
   </si>
@@ -686,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5784,6 +5784,9 @@
       <c r="F222" s="1">
         <v>46106</v>
       </c>
+      <c r="G222" s="1">
+        <v>46114</v>
+      </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
@@ -5830,6 +5833,9 @@
       <c r="F224" s="1">
         <v>46113</v>
       </c>
+      <c r="G224" s="1">
+        <v>46114</v>
+      </c>
       <c r="H224" t="s">
         <v>98</v>
       </c>
@@ -5850,12 +5856,41 @@
       <c r="D225" s="2">
         <v>42382.32</v>
       </c>
+      <c r="E225">
+        <v>339</v>
+      </c>
+      <c r="F225" s="1">
+        <v>46121</v>
+      </c>
       <c r="I225">
         <v>16187</v>
       </c>
     </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226">
+        <v>9</v>
+      </c>
+      <c r="C226" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D226" s="2">
+        <v>168681.47</v>
+      </c>
+      <c r="E226">
+        <v>344</v>
+      </c>
+      <c r="F226" s="1">
+        <v>46120</v>
+      </c>
+      <c r="I226">
+        <v>16012</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A225" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A226" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5362056C-41FF-49E3-BD13-988B873EEC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D016B423-82EC-4C9D-AB30-CFDD7358DF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -5885,6 +5885,9 @@
       <c r="F226" s="1">
         <v>46120</v>
       </c>
+      <c r="G226" s="1">
+        <v>46126</v>
+      </c>
       <c r="I226">
         <v>16012</v>
       </c>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D016B423-82EC-4C9D-AB30-CFDD7358DF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C8A8BB-5681-4F9A-9C74-B92BB4E61245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$227</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="101">
   <si>
     <t>007/2024</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>os = 3.127,65m²/med=2.860,85m²</t>
+  </si>
+  <si>
+    <t>11 do 4</t>
+  </si>
+  <si>
+    <t>os=1.505,62m²/med=1.354,31m²</t>
   </si>
 </sst>
 </file>
@@ -686,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I226"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5892,8 +5898,28 @@
         <v>16012</v>
       </c>
     </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>5</v>
+      </c>
+      <c r="B227" t="s">
+        <v>99</v>
+      </c>
+      <c r="C227" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D227" s="2">
+        <v>315796.65000000002</v>
+      </c>
+      <c r="H227" t="s">
+        <v>100</v>
+      </c>
+      <c r="I227">
+        <v>16374</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A226" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C8A8BB-5681-4F9A-9C74-B92BB4E61245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7016BE-0A28-4B18-99AD-7DE5F9238BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -5868,6 +5868,9 @@
       <c r="F225" s="1">
         <v>46121</v>
       </c>
+      <c r="G225" s="1">
+        <v>46122</v>
+      </c>
       <c r="I225">
         <v>16187</v>
       </c>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7016BE-0A28-4B18-99AD-7DE5F9238BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572445F4-2A64-4289-AC2D-1E0F19BDD940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -332,7 +332,7 @@
     <t>11 do 4</t>
   </si>
   <si>
-    <t>os=1.505,62m²/med=1.354,31m²</t>
+    <t>os=1.459,87m²/med=1.309,59m²</t>
   </si>
 </sst>
 </file>
@@ -5912,7 +5912,13 @@
         <v>46134</v>
       </c>
       <c r="D227" s="2">
-        <v>315796.65000000002</v>
+        <v>305368.88</v>
+      </c>
+      <c r="E227">
+        <v>1147</v>
+      </c>
+      <c r="F227" s="1">
+        <v>46139</v>
       </c>
       <c r="H227" t="s">
         <v>100</v>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572445F4-2A64-4289-AC2D-1E0F19BDD940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566AA0F8-6942-43C1-A32F-723803686620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -692,6 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -735,7 +736,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -758,7 +759,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -781,7 +782,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -804,7 +805,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -957,7 +958,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -983,7 +984,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1009,7 +1010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1035,7 +1036,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1061,7 +1062,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1087,7 +1088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1113,7 +1114,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1185,7 +1186,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1208,7 +1209,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1231,7 +1232,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1277,7 +1278,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1300,7 +1301,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1346,7 +1347,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1369,7 +1370,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1392,7 +1393,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1415,7 +1416,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1461,7 +1462,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1484,7 +1485,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1530,7 +1531,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1554,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1599,7 +1600,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1622,7 +1623,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1691,7 +1692,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1714,7 +1715,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1760,7 +1761,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1783,7 +1784,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1829,7 +1830,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1852,7 +1853,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1898,7 +1899,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1921,7 +1922,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1944,7 +1945,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1967,7 +1968,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1990,7 +1991,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2013,7 +2014,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2036,7 +2037,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2059,7 +2060,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2082,7 +2083,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2105,7 +2106,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2128,7 +2129,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2151,7 +2152,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2197,7 +2198,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2220,7 +2221,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2266,7 +2267,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2289,7 +2290,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2315,7 +2316,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2361,7 +2362,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2407,7 +2408,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2430,7 +2431,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2454,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2467,7 +2468,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2559,7 +2560,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2582,7 +2583,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2651,7 +2652,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2694,7 +2695,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2714,7 +2715,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2734,7 +2735,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2754,7 +2755,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2774,7 +2775,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2794,7 +2795,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2814,7 +2815,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2834,7 +2835,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2860,7 +2861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2912,7 +2913,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2935,7 +2936,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2981,7 +2982,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3004,7 +3005,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3027,7 +3028,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3050,7 +3051,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3073,7 +3074,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3096,7 +3097,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3119,7 +3120,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3142,7 +3143,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3165,7 +3166,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3188,7 +3189,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3234,7 +3235,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3257,7 +3258,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3332,7 +3333,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3349,7 +3350,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3372,7 +3373,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3395,7 +3396,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3441,7 +3442,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3464,7 +3465,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3487,7 +3488,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3510,7 +3511,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3533,7 +3534,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3556,7 +3557,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3579,7 +3580,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3628,7 +3629,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3651,7 +3652,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3674,7 +3675,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3697,7 +3698,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3720,7 +3721,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3743,7 +3744,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3815,7 +3816,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3884,7 +3885,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3910,7 +3911,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -3939,7 +3940,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3962,7 +3963,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -3988,7 +3989,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4037,7 +4038,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4089,7 +4090,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4158,7 +4159,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4265,7 +4266,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4288,7 +4289,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4311,7 +4312,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4337,7 +4338,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4389,7 +4390,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4415,7 +4416,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4441,7 +4442,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4493,7 +4494,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4519,7 +4520,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4571,7 +4572,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4600,7 +4601,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4626,7 +4627,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4649,7 +4650,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4724,7 +4725,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4747,7 +4748,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4802,7 +4803,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4871,7 +4872,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4927,7 +4928,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4941,7 +4942,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4955,7 +4956,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4969,7 +4970,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4983,7 +4984,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4997,7 +4998,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5025,7 +5026,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5053,7 +5054,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5081,7 +5082,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5095,7 +5096,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5123,7 +5124,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5137,7 +5138,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5163,7 +5164,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5189,7 +5190,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5203,7 +5204,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5226,7 +5227,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5275,7 +5276,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5295,7 +5296,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5353,7 +5354,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5379,7 +5380,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5402,7 +5403,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5445,7 +5446,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5471,7 +5472,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5526,7 +5527,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +5553,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5624,7 +5625,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5647,7 +5648,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5670,7 +5671,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5693,7 +5694,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5716,7 +5717,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5771,7 +5772,7 @@
         <v>15869</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -5794,7 +5795,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5849,7 +5850,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5920,6 +5921,9 @@
       <c r="F227" s="1">
         <v>46139</v>
       </c>
+      <c r="G227" s="1">
+        <v>46142</v>
+      </c>
       <c r="H227" t="s">
         <v>100</v>
       </c>
@@ -5928,7 +5932,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="009/2022"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566AA0F8-6942-43C1-A32F-723803686620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE41C2ED-8B3E-41D9-9210-B77E58AD13BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE41C2ED-8B3E-41D9-9210-B77E58AD13BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DD8B74-B3FC-4261-81EC-70B885863A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -692,7 +692,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -736,7 +735,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -759,7 +758,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -782,7 +781,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -805,7 +804,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -958,7 +957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -984,7 +983,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1010,7 +1009,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1036,7 +1035,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1062,7 +1061,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1088,7 +1087,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1114,7 +1113,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1140,7 +1139,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1209,7 +1208,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1232,7 +1231,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1255,7 +1254,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1278,7 +1277,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1301,7 +1300,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1324,7 +1323,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1347,7 +1346,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1370,7 +1369,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1393,7 +1392,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1416,7 +1415,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1462,7 +1461,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1485,7 +1484,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1508,7 +1507,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1531,7 +1530,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1553,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1576,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1600,7 +1599,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1623,7 +1622,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1646,7 +1645,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1669,7 +1668,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1692,7 +1691,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1715,7 +1714,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1738,7 +1737,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1761,7 +1760,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1784,7 +1783,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1830,7 +1829,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1853,7 +1852,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1876,7 +1875,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1922,7 +1921,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1968,7 +1967,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1991,7 +1990,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2014,7 +2013,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2175,7 +2174,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2198,7 +2197,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2244,7 +2243,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2267,7 +2266,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2290,7 +2289,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2316,7 +2315,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2362,7 +2361,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2408,7 +2407,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2431,7 +2430,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2454,7 +2453,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2537,7 +2536,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2560,7 +2559,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2583,7 +2582,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2629,7 +2628,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2652,7 +2651,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2695,7 +2694,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2715,7 +2714,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2755,7 +2754,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2795,7 +2794,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2835,7 +2834,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2861,7 +2860,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2959,7 +2958,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2982,7 +2981,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3005,7 +3004,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3028,7 +3027,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3074,7 +3073,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3120,7 +3119,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3166,7 +3165,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3189,7 +3188,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3258,7 +3257,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3281,7 +3280,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3333,7 +3332,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3350,7 +3349,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3396,7 +3395,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3442,7 +3441,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3465,7 +3464,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3488,7 +3487,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3511,7 +3510,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3534,7 +3533,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3557,7 +3556,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3580,7 +3579,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3629,7 +3628,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3652,7 +3651,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3675,7 +3674,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3721,7 +3720,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3744,7 +3743,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3767,7 +3766,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3793,7 +3792,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3816,7 +3815,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3862,7 +3861,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3885,7 +3884,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -3940,7 +3939,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3963,7 +3962,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -3989,7 +3988,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -4015,7 +4014,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4038,7 +4037,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4064,7 +4063,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4090,7 +4089,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4139,7 +4138,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4159,7 +4158,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4185,7 +4184,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4214,7 +4213,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4266,7 +4265,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4289,7 +4288,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4312,7 +4311,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4338,7 +4337,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4364,7 +4363,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4390,7 +4389,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4416,7 +4415,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4442,7 +4441,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4494,7 +4493,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4572,7 +4571,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4601,7 +4600,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4627,7 +4626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4650,7 +4649,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4676,7 +4675,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4725,7 +4724,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4748,7 +4747,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4777,7 +4776,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4803,7 +4802,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4858,7 +4857,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4872,7 +4871,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4886,7 +4885,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4900,7 +4899,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4914,7 +4913,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4928,7 +4927,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4942,7 +4941,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4956,7 +4955,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4970,7 +4969,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4984,7 +4983,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4998,7 +4997,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -5012,7 +5011,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5026,7 +5025,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5040,7 +5039,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5054,7 +5053,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5068,7 +5067,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5082,7 +5081,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5096,7 +5095,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5110,7 +5109,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5124,7 +5123,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5138,7 +5137,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5164,7 +5163,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5190,7 +5189,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5204,7 +5203,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5227,7 +5226,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5250,7 +5249,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5296,7 +5295,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5354,7 +5353,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5380,7 +5379,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5403,7 +5402,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5426,7 +5425,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5446,7 +5445,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5472,7 +5471,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5527,7 +5526,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5553,7 +5552,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5579,7 +5578,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5602,7 +5601,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5625,7 +5624,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5648,7 +5647,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5671,7 +5670,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5694,7 +5693,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5717,7 +5716,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5772,7 +5771,7 @@
         <v>15869</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -5795,7 +5794,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5850,7 +5849,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5876,7 +5875,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5932,13 +5931,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="009/2022"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DD8B74-B3FC-4261-81EC-70B885863A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0AD99F-05E0-4017-AE07-F6AB1597E4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicoes" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="101">
   <si>
     <t>007/2024</t>
   </si>
@@ -5938,7 +5938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7729,6 +7729,29 @@
         <v>46233</v>
       </c>
     </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46097</v>
+      </c>
+      <c r="E92" s="1">
+        <v>46099</v>
+      </c>
+      <c r="F92" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G92" s="1">
+        <v>46190</v>
+      </c>
+      <c r="H92" s="1">
+        <v>46309</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I91" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0AD99F-05E0-4017-AE07-F6AB1597E4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47DE805-0434-4A67-AAC2-BFFFAE003A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicoes" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="103">
   <si>
     <t>007/2024</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>os=1.459,87m²/med=1.309,59m²</t>
+  </si>
+  <si>
+    <t>1 do 5</t>
+  </si>
+  <si>
+    <t>os=4.159,71m²/med=3.828,35m²</t>
   </si>
 </sst>
 </file>
@@ -371,13 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,7 +699,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I227"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -735,7 +743,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -758,7 +766,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -781,7 +789,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -804,7 +812,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -957,7 +965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -983,7 +991,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1009,7 +1017,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1035,7 +1043,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1061,7 +1069,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1087,7 +1095,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1113,7 +1121,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1139,7 +1147,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1185,7 +1193,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1208,7 +1216,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1231,7 +1239,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1254,7 +1262,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1277,7 +1285,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1300,7 +1308,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1323,7 +1331,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1346,7 +1354,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1369,7 +1377,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1392,7 +1400,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1415,7 +1423,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1438,7 +1446,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1461,7 +1469,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1484,7 +1492,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1507,7 +1515,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1530,7 +1538,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1561,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1584,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1599,7 +1607,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1622,7 +1630,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1645,7 +1653,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1668,7 +1676,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1691,7 +1699,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1714,7 +1722,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1737,7 +1745,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1760,7 +1768,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1783,7 +1791,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1806,7 +1814,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1829,7 +1837,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1852,7 +1860,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1875,7 +1883,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1898,7 +1906,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1921,7 +1929,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1944,7 +1952,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1967,7 +1975,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1990,7 +1998,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2013,7 +2021,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2036,7 +2044,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2059,7 +2067,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2082,7 +2090,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2105,7 +2113,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2128,7 +2136,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2151,7 +2159,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2174,7 +2182,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2197,7 +2205,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2220,7 +2228,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2243,7 +2251,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2266,7 +2274,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2289,7 +2297,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2315,7 +2323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2338,7 +2346,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2361,7 +2369,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2384,7 +2392,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2407,7 +2415,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2430,7 +2438,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2461,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2467,7 +2475,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2536,7 +2544,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2559,7 +2567,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2582,7 +2590,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2605,7 +2613,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2628,7 +2636,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2651,7 +2659,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2694,7 +2702,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2714,7 +2722,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2734,7 +2742,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2754,7 +2762,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2774,7 +2782,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2814,7 +2822,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2834,7 +2842,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2860,7 +2868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2912,7 +2920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2935,7 +2943,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2958,7 +2966,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2981,7 +2989,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3004,7 +3012,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3027,7 +3035,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3050,7 +3058,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3096,7 +3104,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3119,7 +3127,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3142,7 +3150,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3165,7 +3173,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3188,7 +3196,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3211,7 +3219,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3234,7 +3242,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3257,7 +3265,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3280,7 +3288,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3332,7 +3340,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3349,7 +3357,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3372,7 +3380,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3395,7 +3403,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3441,7 +3449,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3464,7 +3472,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3487,7 +3495,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3510,7 +3518,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3533,7 +3541,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3579,7 +3587,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3628,7 +3636,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3651,7 +3659,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3674,7 +3682,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3697,7 +3705,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3720,7 +3728,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3743,7 +3751,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3766,7 +3774,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3792,7 +3800,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3815,7 +3823,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3861,7 +3869,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3884,7 +3892,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3910,7 +3918,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -3939,7 +3947,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3962,7 +3970,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -3988,7 +3996,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -4014,7 +4022,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4037,7 +4045,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4063,7 +4071,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4089,7 +4097,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4138,7 +4146,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4158,7 +4166,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4184,7 +4192,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4213,7 +4221,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4265,7 +4273,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4288,7 +4296,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4311,7 +4319,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4337,7 +4345,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4363,7 +4371,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4389,7 +4397,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4415,7 +4423,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4441,7 +4449,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4467,7 +4475,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4493,7 +4501,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4519,7 +4527,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4545,7 +4553,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4571,7 +4579,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4600,7 +4608,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4626,7 +4634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4649,7 +4657,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4675,7 +4683,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4724,7 +4732,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4747,7 +4755,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4776,7 +4784,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4802,7 +4810,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4857,7 +4865,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4871,7 +4879,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4885,7 +4893,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4899,7 +4907,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4913,7 +4921,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4927,7 +4935,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4941,7 +4949,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4955,7 +4963,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4969,7 +4977,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4983,7 +4991,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -4997,7 +5005,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -5011,7 +5019,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5025,7 +5033,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5039,7 +5047,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5053,7 +5061,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5067,7 +5075,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5081,7 +5089,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5095,7 +5103,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5109,7 +5117,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5123,7 +5131,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5137,7 +5145,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5163,7 +5171,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5189,7 +5197,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5203,7 +5211,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5226,7 +5234,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5249,7 +5257,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5275,7 +5283,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5295,7 +5303,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5353,7 +5361,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5379,7 +5387,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5402,7 +5410,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5425,7 +5433,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5445,7 +5453,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5471,7 +5479,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5526,7 +5534,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +5560,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5578,7 +5586,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5601,7 +5609,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5624,7 +5632,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5647,7 +5655,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5670,7 +5678,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5693,7 +5701,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5716,7 +5724,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5771,7 +5779,7 @@
         <v>15869</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -5794,7 +5802,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5849,7 +5857,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5875,7 +5883,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5930,15 +5938,41 @@
         <v>16374</v>
       </c>
     </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>5</v>
+      </c>
+      <c r="B228" t="s">
+        <v>101</v>
+      </c>
+      <c r="C228" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D228" s="2">
+        <v>925350.92</v>
+      </c>
+      <c r="H228" t="s">
+        <v>102</v>
+      </c>
+      <c r="I228">
+        <v>16853</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="009/2022"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7752,6 +7786,35 @@
         <v>46309</v>
       </c>
     </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" t="s">
+        <v>52</v>
+      </c>
+      <c r="C93" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D93">
+        <v>307076.65000000002</v>
+      </c>
+      <c r="E93" s="1">
+        <v>46150</v>
+      </c>
+      <c r="F93" s="1">
+        <v>46514</v>
+      </c>
+      <c r="G93" s="1">
+        <v>46205</v>
+      </c>
+      <c r="H93" s="1">
+        <v>46584</v>
+      </c>
+      <c r="I93" s="6">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I91" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47DE805-0434-4A67-AAC2-BFFFAE003A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3ADFB6C-0E39-442E-A569-F73422C1BB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicoes" sheetId="2" r:id="rId1"/>
     <sheet name="Aditivo" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$227</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="103">
   <si>
     <t>007/2024</t>
   </si>
@@ -377,14 +377,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5972,7 +5971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7811,12 +7810,29 @@
       <c r="H93" s="1">
         <v>46584</v>
       </c>
-      <c r="I93" s="6">
+      <c r="I93">
         <v>4.1100000000000003</v>
       </c>
     </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" s="1">
+        <v>46101</v>
+      </c>
+      <c r="E94" s="1">
+        <v>46112</v>
+      </c>
+      <c r="F94" s="1">
+        <v>46201</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I91" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}"/>
+  <autoFilter ref="A1:I94" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3ADFB6C-0E39-442E-A569-F73422C1BB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264180A7-3B24-445E-86A5-EE6DE1FA36D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicoes" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$228</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="103">
   <si>
     <t>007/2024</t>
   </si>
@@ -699,7 +699,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -834,7 +834,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -860,7 +860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -886,7 +886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -912,7 +912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -938,7 +938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>15927</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>16012</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>16374</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5950,6 +5950,12 @@
       <c r="D228" s="2">
         <v>925350.92</v>
       </c>
+      <c r="E228">
+        <v>1179</v>
+      </c>
+      <c r="F228" s="1">
+        <v>46175</v>
+      </c>
       <c r="H228" t="s">
         <v>102</v>
       </c>
@@ -5957,11 +5963,48 @@
         <v>16853</v>
       </c>
     </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>57</v>
+      </c>
+      <c r="B229">
+        <v>46</v>
+      </c>
+      <c r="C229" s="1">
+        <v>46064</v>
+      </c>
+      <c r="D229" s="2">
+        <v>57532.81</v>
+      </c>
+      <c r="E229">
+        <v>1019</v>
+      </c>
+      <c r="F229" s="1">
+        <v>46175</v>
+      </c>
+      <c r="G229" s="1">
+        <v>46176</v>
+      </c>
+      <c r="I229">
+        <v>15710</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>57</v>
+      </c>
+      <c r="B230">
+        <v>47</v>
+      </c>
+      <c r="C230" s="1">
+        <v>46087</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A227" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:A228" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="009/2022"/>
+        <filter val="004/2022"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5971,6 +6014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6015,7 +6059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -6045,7 +6089,7 @@
         <v>0.17083016949152541</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6059,7 +6103,7 @@
         <v>22686.63</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6076,7 +6120,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6220,7 +6264,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -6240,7 +6284,7 @@
         <v>45484</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -6255,7 +6299,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -6278,7 +6322,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -6295,7 +6339,7 @@
         <v>12.5153</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -6312,7 +6356,7 @@
         <v>7.4950000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -6329,7 +6373,7 @@
         <v>20.66</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -6352,7 +6396,7 @@
         <v>45696</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -6363,7 +6407,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -6386,7 +6430,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -6412,7 +6456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -6429,7 +6473,7 @@
         <v>17.348874299999999</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -6437,7 +6481,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -6451,7 +6495,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -6471,7 +6515,7 @@
         <v>45604</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -6485,7 +6529,7 @@
         <v>37.103999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -6499,7 +6543,7 @@
         <v>3.2429999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -6513,7 +6557,7 @@
         <v>51.812800000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -6533,7 +6577,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -6556,7 +6600,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -6573,7 +6617,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -6590,7 +6634,7 @@
         <v>45687</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -6601,7 +6645,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -6624,7 +6668,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -6647,7 +6691,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -6664,7 +6708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -6681,7 +6725,7 @@
         <v>45330</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -6704,7 +6748,7 @@
         <v>45539</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -6727,7 +6771,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -6750,7 +6794,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -6773,7 +6817,7 @@
         <v>45900</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -6796,7 +6840,7 @@
         <v>46020</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -6813,7 +6857,7 @@
         <v>45798</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -6830,7 +6874,7 @@
         <v>45918</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -6853,7 +6897,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -6876,7 +6920,7 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -6896,7 +6940,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -6904,7 +6948,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -6924,7 +6968,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -6938,7 +6982,7 @@
         <v>24.927</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -6958,7 +7002,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -6972,7 +7016,7 @@
         <v>24.622599999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -6995,7 +7039,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -7012,7 +7056,7 @@
         <v>3.5918095000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -7029,7 +7073,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -7052,7 +7096,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -7069,7 +7113,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -7086,7 +7130,7 @@
         <v>45837</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -7109,7 +7153,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -7132,7 +7176,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -7155,7 +7199,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -7172,7 +7216,7 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -7195,7 +7239,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -7206,7 +7250,7 @@
         <v>45840</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -7223,7 +7267,7 @@
         <v>48.59</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -7237,7 +7281,7 @@
         <v>45183</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>60</v>
       </c>
@@ -7257,7 +7301,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>60</v>
       </c>
@@ -7271,7 +7315,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>60</v>
       </c>
@@ -7297,7 +7341,7 @@
         <v>44390</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>60</v>
       </c>
@@ -7311,7 +7355,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>62</v>
       </c>
@@ -7331,7 +7375,7 @@
         <v>46040</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>62</v>
       </c>
@@ -7345,7 +7389,7 @@
         <v>4.7679</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -7368,7 +7412,7 @@
         <v>45305</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -7391,7 +7435,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -7414,7 +7458,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -7437,7 +7481,7 @@
         <v>45791</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -7460,7 +7504,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -7480,7 +7524,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -7503,7 +7547,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -7532,7 +7576,7 @@
         <v>19.106356999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>2</v>
       </c>
@@ -7555,7 +7599,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -7578,7 +7622,7 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -7601,7 +7645,7 @@
         <v>46156</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -7624,7 +7668,7 @@
         <v>46426</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1</v>
       </c>
@@ -7647,7 +7691,7 @@
         <v>46376</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -7670,7 +7714,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -7693,7 +7737,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -7716,7 +7760,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -7739,7 +7783,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -7762,7 +7806,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>9</v>
       </c>
@@ -7814,7 +7858,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -7832,7 +7876,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I94" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}"/>
+  <autoFilter ref="A1:I94" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="009/2022"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264180A7-3B24-445E-86A5-EE6DE1FA36D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E503077A-DE5D-4C0D-A2A0-15FB02F89C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$231</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="104">
   <si>
     <t>007/2024</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>os=4.159,71m²/med=3.828,35m²</t>
+  </si>
+  <si>
+    <t>010/2026</t>
   </si>
 </sst>
 </file>
@@ -699,7 +702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I230"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -964,7 +967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -990,7 +993,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1146,7 +1149,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -3287,7 +3290,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3773,7 +3776,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3917,7 +3920,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4191,7 +4194,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4578,7 +4581,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4656,7 +4659,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4783,7 +4786,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -5170,7 +5173,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5196,7 +5199,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5409,7 +5412,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5478,7 +5481,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5559,7 +5562,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5723,7 +5726,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5801,7 +5804,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5856,7 +5859,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5963,7 +5966,7 @@
         <v>16853</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>57</v>
       </c>
@@ -5989,7 +5992,7 @@
         <v>15710</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>57</v>
       </c>
@@ -6000,11 +6003,42 @@
         <v>46087</v>
       </c>
     </row>
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>103</v>
+      </c>
+      <c r="B231">
+        <v>1</v>
+      </c>
+      <c r="C231" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D231" s="2">
+        <v>29600</v>
+      </c>
+      <c r="I231">
+        <v>16828</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>1</v>
+      </c>
+      <c r="B232">
+        <v>24</v>
+      </c>
+      <c r="C232" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D232" s="2">
+        <v>31601.21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A228" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:A231" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="004/2022"/>
+        <filter val="028/2023"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E503077A-DE5D-4C0D-A2A0-15FB02F89C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75283B3F-C9A8-4D2D-8F62-97EE72B8A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$232</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -837,7 +837,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -863,7 +863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -889,7 +889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -941,7 +941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -967,7 +967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -993,7 +993,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>15927</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>16012</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>16374</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5958,6 +5958,9 @@
       </c>
       <c r="F228" s="1">
         <v>46175</v>
+      </c>
+      <c r="G228" s="1">
+        <v>46176</v>
       </c>
       <c r="H228" t="s">
         <v>102</v>
@@ -6020,7 +6023,7 @@
         <v>16828</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1</v>
       </c>
@@ -6035,10 +6038,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A231" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:A232" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="028/2023"/>
+        <filter val="009/2022"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75283B3F-C9A8-4D2D-8F62-97EE72B8A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CCAB58-64D3-4EC5-9F16-6CB63159C782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -837,7 +837,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -863,7 +863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -889,7 +889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -941,7 +941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -967,7 +967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -993,7 +993,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>15927</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>16012</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>16374</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>16828</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1</v>
       </c>
@@ -6035,13 +6035,22 @@
       </c>
       <c r="D232" s="2">
         <v>31601.21</v>
+      </c>
+      <c r="E232">
+        <v>345</v>
+      </c>
+      <c r="F232" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G232" s="1">
+        <v>46185</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A232" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="009/2022"/>
+        <filter val="028/2023"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CCAB58-64D3-4EC5-9F16-6CB63159C782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B012B023-DD37-4820-87E9-9B0739155CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -6045,6 +6045,9 @@
       <c r="G232" s="1">
         <v>46185</v>
       </c>
+      <c r="I232">
+        <v>16913</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A232" xr:uid="{00000000-0009-0000-0000-000003000000}">

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B012B023-DD37-4820-87E9-9B0739155CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E6DD57-724C-4C1C-A67D-1E5949D65BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -967,7 +967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -993,7 +993,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>103</v>
       </c>
@@ -6019,11 +6019,20 @@
       <c r="D231" s="2">
         <v>29600</v>
       </c>
+      <c r="E231">
+        <v>12</v>
+      </c>
+      <c r="F231" s="1">
+        <v>46182</v>
+      </c>
+      <c r="G231" s="1">
+        <v>46185</v>
+      </c>
       <c r="I231">
         <v>16828</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1</v>
       </c>
@@ -6053,7 +6062,7 @@
   <autoFilter ref="A1:A232" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="028/2023"/>
+        <filter val="010/2026"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E6DD57-724C-4C1C-A67D-1E5949D65BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D3241A-E75A-4B43-B7C1-9E23D07CB3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="104">
   <si>
     <t>007/2024</t>
   </si>
@@ -702,7 +702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I232"/>
+  <dimension ref="A1:I233"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2092,7 +2092,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>103</v>
       </c>
@@ -6056,13 +6056,30 @@
       </c>
       <c r="I232">
         <v>16913</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>6</v>
+      </c>
+      <c r="B233">
+        <v>10</v>
+      </c>
+      <c r="C233" s="1">
+        <v>46185</v>
+      </c>
+      <c r="D233" s="2">
+        <v>124700.33</v>
+      </c>
+      <c r="I233">
+        <v>16988</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A232" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="010/2026"/>
+        <filter val="018/2024"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D3241A-E75A-4B43-B7C1-9E23D07CB3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDB83AF-00F1-496F-9FBC-E3BC1B2606F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$234</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="106">
   <si>
     <t>007/2024</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>010/2026</t>
+  </si>
+  <si>
+    <t>2 do 5</t>
+  </si>
+  <si>
+    <t>os=2.392,31m²/med=2.226,57m²</t>
   </si>
 </sst>
 </file>
@@ -702,7 +708,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -837,7 +843,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -863,7 +869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -889,7 +895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -941,7 +947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2092,7 +2098,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2325,7 +2331,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2500,7 +2506,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2684,7 +2690,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3319,7 +3325,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3359,7 +3365,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3428,7 +3434,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3615,7 +3621,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3825,7 +3831,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3848,7 +3854,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -4122,7 +4128,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4223,7 +4229,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4249,7 +4255,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4321,7 +4327,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4708,7 +4714,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4838,7 +4844,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5334,7 +5340,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5363,7 +5369,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5507,7 +5513,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5536,7 +5542,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5752,7 +5758,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5830,7 +5836,7 @@
         <v>15927</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5885,7 +5891,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5911,7 +5917,7 @@
         <v>16012</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5940,7 +5946,7 @@
         <v>16374</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -6058,7 +6064,7 @@
         <v>16913</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -6071,15 +6077,41 @@
       <c r="D233" s="2">
         <v>124700.33</v>
       </c>
+      <c r="E233">
+        <v>365</v>
+      </c>
+      <c r="F233" s="1">
+        <v>46195</v>
+      </c>
       <c r="I233">
         <v>16988</v>
       </c>
     </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>5</v>
+      </c>
+      <c r="B234" t="s">
+        <v>104</v>
+      </c>
+      <c r="C234" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D234" s="2">
+        <v>538184.49</v>
+      </c>
+      <c r="H234" t="s">
+        <v>105</v>
+      </c>
+      <c r="I234">
+        <v>17132</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A232" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:A234" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="018/2024"/>
+        <filter val="009/2022"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDB83AF-00F1-496F-9FBC-E3BC1B2606F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06893BA8-B324-4BB5-A5D0-89300EBE6B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$236</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="107">
   <si>
     <t>007/2024</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>os=2.392,31m²/med=2.226,57m²</t>
+  </si>
+  <si>
+    <t>004/2026</t>
   </si>
 </sst>
 </file>
@@ -707,8 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:I234"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -751,7 +753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -774,7 +776,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -797,7 +799,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -820,7 +822,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -973,7 +975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -999,7 +1001,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1025,7 +1027,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1051,7 +1053,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1077,7 +1079,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1103,7 +1105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1129,7 +1131,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1155,7 +1157,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1201,7 +1203,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1224,7 +1226,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1247,7 +1249,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1270,7 +1272,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1293,7 +1295,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1316,7 +1318,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1339,7 +1341,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1362,7 +1364,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1385,7 +1387,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1408,7 +1410,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1431,7 +1433,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1454,7 +1456,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1477,7 +1479,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1500,7 +1502,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1523,7 +1525,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1546,7 +1548,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1569,7 +1571,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1592,7 +1594,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1615,7 +1617,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1638,7 +1640,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1661,7 +1663,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1684,7 +1686,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1707,7 +1709,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1730,7 +1732,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1753,7 +1755,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1776,7 +1778,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1799,7 +1801,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1822,7 +1824,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1845,7 +1847,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1868,7 +1870,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1891,7 +1893,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1914,7 +1916,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1937,7 +1939,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1960,7 +1962,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1983,7 +1985,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -2006,7 +2008,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2029,7 +2031,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2052,7 +2054,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2075,7 +2077,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2098,7 +2100,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2121,7 +2123,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2144,7 +2146,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2167,7 +2169,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2190,7 +2192,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2213,7 +2215,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2236,7 +2238,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2259,7 +2261,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2282,7 +2284,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2305,7 +2307,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2331,7 +2333,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2354,7 +2356,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2377,7 +2379,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2400,7 +2402,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2423,7 +2425,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2446,7 +2448,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2469,7 +2471,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2483,7 +2485,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2552,7 +2554,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2575,7 +2577,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2598,7 +2600,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2621,7 +2623,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2644,7 +2646,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2667,7 +2669,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2710,7 +2712,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2730,7 +2732,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2750,7 +2752,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2770,7 +2772,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2790,7 +2792,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2810,7 +2812,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2830,7 +2832,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2850,7 +2852,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2876,7 +2878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2902,7 +2904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2928,7 +2930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2951,7 +2953,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2974,7 +2976,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2997,7 +2999,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3020,7 +3022,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3043,7 +3045,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3066,7 +3068,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3089,7 +3091,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3112,7 +3114,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3135,7 +3137,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3158,7 +3160,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3181,7 +3183,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3204,7 +3206,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3227,7 +3229,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3250,7 +3252,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3273,7 +3275,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3296,7 +3298,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3348,7 +3350,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3365,7 +3367,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3388,7 +3390,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3411,7 +3413,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3457,7 +3459,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3480,7 +3482,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3503,7 +3505,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3526,7 +3528,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3549,7 +3551,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3572,7 +3574,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3595,7 +3597,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3644,7 +3646,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3667,7 +3669,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3690,7 +3692,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3713,7 +3715,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3736,7 +3738,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3759,7 +3761,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3782,7 +3784,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3808,7 +3810,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3831,7 +3833,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3877,7 +3879,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3900,7 +3902,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3926,7 +3928,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -3955,7 +3957,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3978,7 +3980,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -4004,7 +4006,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -4030,7 +4032,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4053,7 +4055,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4079,7 +4081,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4105,7 +4107,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4154,7 +4156,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4174,7 +4176,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4200,7 +4202,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4229,7 +4231,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4281,7 +4283,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4304,7 +4306,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4327,7 +4329,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4353,7 +4355,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4379,7 +4381,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4405,7 +4407,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4431,7 +4433,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4457,7 +4459,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4483,7 +4485,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4509,7 +4511,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4535,7 +4537,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4561,7 +4563,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4587,7 +4589,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4616,7 +4618,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4642,7 +4644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4665,7 +4667,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4691,7 +4693,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4740,7 +4742,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4763,7 +4765,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4792,7 +4794,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4818,7 +4820,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4873,7 +4875,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4887,7 +4889,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4901,7 +4903,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4915,7 +4917,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4929,7 +4931,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4943,7 +4945,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4957,7 +4959,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4971,7 +4973,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4985,7 +4987,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -4999,7 +5001,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -5013,7 +5015,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -5027,7 +5029,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5041,7 +5043,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5055,7 +5057,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5069,7 +5071,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5083,7 +5085,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5097,7 +5099,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5111,7 +5113,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5125,7 +5127,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5139,7 +5141,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5153,7 +5155,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5179,7 +5181,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5205,7 +5207,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5219,7 +5221,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5242,7 +5244,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5265,7 +5267,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5291,7 +5293,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5311,7 +5313,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5369,7 +5371,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5395,7 +5397,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5418,7 +5420,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5441,7 +5443,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5461,7 +5463,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5487,7 +5489,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5542,7 +5544,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5568,7 +5570,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5594,7 +5596,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5617,7 +5619,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5640,7 +5642,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5663,7 +5665,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5686,7 +5688,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5709,7 +5711,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5732,7 +5734,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5787,7 +5789,7 @@
         <v>15869</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -5810,7 +5812,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5865,7 +5867,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5891,7 +5893,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5975,7 +5977,7 @@
         <v>16853</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>57</v>
       </c>
@@ -6001,7 +6003,7 @@
         <v>15710</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>57</v>
       </c>
@@ -6012,7 +6014,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>103</v>
       </c>
@@ -6038,7 +6040,7 @@
         <v>16828</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1</v>
       </c>
@@ -6064,7 +6066,7 @@
         <v>16913</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -6082,6 +6084,9 @@
       </c>
       <c r="F233" s="1">
         <v>46195</v>
+      </c>
+      <c r="G233" s="1">
+        <v>46206</v>
       </c>
       <c r="I233">
         <v>16988</v>
@@ -6100,6 +6105,15 @@
       <c r="D234" s="2">
         <v>538184.49</v>
       </c>
+      <c r="E234">
+        <v>1193</v>
+      </c>
+      <c r="F234" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G234" s="1">
+        <v>46206</v>
+      </c>
       <c r="H234" t="s">
         <v>105</v>
       </c>
@@ -6107,14 +6121,65 @@
         <v>17132</v>
       </c>
     </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>12</v>
+      </c>
+      <c r="B235">
+        <v>21</v>
+      </c>
+      <c r="C235" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D235" s="2">
+        <v>43977.55</v>
+      </c>
+      <c r="I235">
+        <v>17232</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>1</v>
+      </c>
+      <c r="B236">
+        <v>25</v>
+      </c>
+      <c r="C236" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D236" s="2">
+        <v>15001.95</v>
+      </c>
+      <c r="I236">
+        <v>17230</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>106</v>
+      </c>
+      <c r="B237">
+        <v>1</v>
+      </c>
+      <c r="C237" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D237" s="2">
+        <v>1784525.37</v>
+      </c>
+      <c r="E237">
+        <v>782</v>
+      </c>
+      <c r="F237" s="1">
+        <v>46204</v>
+      </c>
+      <c r="G237" s="1">
+        <v>46206</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A234" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="009/2022"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:A236" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06893BA8-B324-4BB5-A5D0-89300EBE6B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C099ECA-A6E4-4FAE-850F-585D6A8AC58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -6134,6 +6134,12 @@
       <c r="D235" s="2">
         <v>43977.55</v>
       </c>
+      <c r="E235">
+        <v>348</v>
+      </c>
+      <c r="F235" s="1">
+        <v>46211</v>
+      </c>
       <c r="I235">
         <v>17232</v>
       </c>
@@ -6150,6 +6156,12 @@
       </c>
       <c r="D236" s="2">
         <v>15001.95</v>
+      </c>
+      <c r="E236">
+        <v>349</v>
+      </c>
+      <c r="F236" s="1">
+        <v>46211</v>
       </c>
       <c r="I236">
         <v>17230</v>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C099ECA-A6E4-4FAE-850F-585D6A8AC58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B45FD37-D34C-4D20-BE31-7A41EDB436C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicoes" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="107">
   <si>
     <t>007/2024</t>
   </si>
@@ -6199,7 +6199,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -6321,7 +6321,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6360,7 +6360,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>24.704439699999998</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>45840</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>46309</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -8057,13 +8057,36 @@
       </c>
       <c r="F94" s="1">
         <v>46201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" s="1">
+        <v>46101</v>
+      </c>
+      <c r="E95" s="1">
+        <v>46108</v>
+      </c>
+      <c r="F95" s="1">
+        <v>46472</v>
+      </c>
+      <c r="G95" s="1">
+        <v>46108</v>
+      </c>
+      <c r="H95" s="1">
+        <v>46472</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I94" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
     <filterColumn colId="0">
       <filters>
-        <filter val="009/2022"/>
+        <filter val="007/2024"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B45FD37-D34C-4D20-BE31-7A41EDB436C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8281563E-13FF-4BCB-A625-9C65688895EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicoes" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$239</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="107">
   <si>
     <t>007/2024</t>
   </si>
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -6163,6 +6163,9 @@
       <c r="F236" s="1">
         <v>46211</v>
       </c>
+      <c r="G236" s="1">
+        <v>46213</v>
+      </c>
       <c r="I236">
         <v>17230</v>
       </c>
@@ -6190,8 +6193,51 @@
         <v>46206</v>
       </c>
     </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>1</v>
+      </c>
+      <c r="B238">
+        <v>26</v>
+      </c>
+      <c r="C238" s="1">
+        <v>46219</v>
+      </c>
+      <c r="D238" s="2">
+        <v>45911.199999999997</v>
+      </c>
+      <c r="E238">
+        <v>350</v>
+      </c>
+      <c r="F238" s="1">
+        <v>46225</v>
+      </c>
+      <c r="I238">
+        <v>17378</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>103</v>
+      </c>
+      <c r="B239">
+        <v>2</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D239" s="2">
+        <v>29600</v>
+      </c>
+      <c r="E239">
+        <v>13</v>
+      </c>
+      <c r="F239" s="1">
+        <v>46224</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A236" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A239" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8281563E-13FF-4BCB-A625-9C65688895EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F95FDB-4004-4D73-B72A-33F64CE33659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="109">
   <si>
     <t>007/2024</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>004/2026</t>
+  </si>
+  <si>
+    <t>3 do 5</t>
+  </si>
+  <si>
+    <t>os=2.861,45m² / med=2.663,42m²</t>
   </si>
 </sst>
 </file>
@@ -710,7 +716,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
-  <dimension ref="A1:I239"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -753,7 +760,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -776,7 +783,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -799,7 +806,7 @@
         <v>45511</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -822,7 +829,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -845,7 +852,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -871,7 +878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -897,7 +904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -923,7 +930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -949,7 +956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1180,7 +1187,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1203,7 +1210,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1226,7 +1233,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1249,7 +1256,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1272,7 +1279,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1295,7 +1302,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1318,7 +1325,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1341,7 +1348,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1364,7 +1371,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1387,7 +1394,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1410,7 +1417,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1433,7 +1440,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1456,7 +1463,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1479,7 +1486,7 @@
         <v>45456</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1502,7 +1509,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1525,7 +1532,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1548,7 +1555,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1571,7 +1578,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1601,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1617,7 +1624,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1640,7 +1647,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -1663,7 +1670,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -1686,7 +1693,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -1709,7 +1716,7 @@
         <v>44990</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -1732,7 +1739,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1755,7 +1762,7 @@
         <v>45427</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1778,7 +1785,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1801,7 +1808,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1824,7 +1831,7 @@
         <v>45463</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1847,7 +1854,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1870,7 +1877,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1893,7 +1900,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1916,7 +1923,7 @@
         <v>45589</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1939,7 +1946,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1962,7 +1969,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1992,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -2008,7 +2015,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2038,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2054,7 +2061,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2077,7 +2084,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2100,7 +2107,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2123,7 +2130,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2146,7 +2153,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -2169,7 +2176,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -2192,7 +2199,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2215,7 +2222,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2238,7 +2245,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2261,7 +2268,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2284,7 +2291,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2333,7 +2340,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2356,7 +2363,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2379,7 +2386,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -2402,7 +2409,7 @@
         <v>45595</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -2425,7 +2432,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -2448,7 +2455,7 @@
         <v>45706</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -2471,7 +2478,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2485,7 +2492,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -2508,7 +2515,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2531,7 +2538,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2554,7 +2561,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2584,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
@@ -2600,7 +2607,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -2623,7 +2630,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2646,7 +2653,7 @@
         <v>44523</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2669,7 +2676,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -2692,7 +2699,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -2712,7 +2719,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -2732,7 +2739,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -2752,7 +2759,7 @@
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -2772,7 +2779,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -2792,7 +2799,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -2812,7 +2819,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -2832,7 +2839,7 @@
         <v>45728</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -2852,7 +2859,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -2878,7 +2885,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -2904,7 +2911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -2930,7 +2937,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -2953,7 +2960,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -2976,7 +2983,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -2999,7 +3006,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3045,7 +3052,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3068,7 +3075,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3091,7 +3098,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3114,7 +3121,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3137,7 +3144,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3160,7 +3167,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3183,7 +3190,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3206,7 +3213,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3229,7 +3236,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -3252,7 +3259,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -3275,7 +3282,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2</v>
       </c>
@@ -3327,7 +3334,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3350,7 +3357,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -3367,7 +3374,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3390,7 +3397,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -3413,7 +3420,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -3436,7 +3443,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3459,7 +3466,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3482,7 +3489,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3505,7 +3512,7 @@
         <v>45799</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2</v>
       </c>
@@ -3528,7 +3535,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3551,7 +3558,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -3574,7 +3581,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3597,7 +3604,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -3623,7 +3630,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3646,7 +3653,7 @@
         <v>45812</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -3669,7 +3676,7 @@
         <v>45818</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2</v>
       </c>
@@ -3692,7 +3699,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2</v>
       </c>
@@ -3715,7 +3722,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3738,7 +3745,7 @@
         <v>45790</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3761,7 +3768,7 @@
         <v>45544</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -3810,7 +3817,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -3833,7 +3840,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -3856,7 +3863,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3879,7 +3886,7 @@
         <v>45841</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -3902,7 +3909,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2</v>
       </c>
@@ -3957,7 +3964,7 @@
         <v>13435</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -3980,7 +3987,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2</v>
       </c>
@@ -4006,7 +4013,7 @@
         <v>13526</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2</v>
       </c>
@@ -4032,7 +4039,7 @@
         <v>13525</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4055,7 +4062,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -4081,7 +4088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -4107,7 +4114,7 @@
         <v>13578</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2</v>
       </c>
@@ -4130,7 +4137,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4156,7 +4163,7 @@
         <v>13747</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -4176,7 +4183,7 @@
         <v>13757</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -4231,7 +4238,7 @@
         <v>13962</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -4257,7 +4264,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4283,7 +4290,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>7</v>
       </c>
@@ -4306,7 +4313,7 @@
         <v>14110</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -4329,7 +4336,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -4355,7 +4362,7 @@
         <v>14221</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>58</v>
       </c>
@@ -4381,7 +4388,7 @@
         <v>12856</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -4407,7 +4414,7 @@
         <v>12857</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>58</v>
       </c>
@@ -4433,7 +4440,7 @@
         <v>12858</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>58</v>
       </c>
@@ -4459,7 +4466,7 @@
         <v>12859</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>58</v>
       </c>
@@ -4485,7 +4492,7 @@
         <v>12860</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>58</v>
       </c>
@@ -4511,7 +4518,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4537,7 +4544,7 @@
         <v>13337</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>58</v>
       </c>
@@ -4563,7 +4570,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>58</v>
       </c>
@@ -4618,7 +4625,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -4644,7 +4651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>58</v>
       </c>
@@ -4693,7 +4700,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -4716,7 +4723,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4742,7 +4749,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -4765,7 +4772,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -4820,7 +4827,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -4846,7 +4853,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -4875,7 +4882,7 @@
         <v>14754</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -4889,7 +4896,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -4903,7 +4910,7 @@
         <v>175544.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>62</v>
       </c>
@@ -4917,7 +4924,7 @@
         <v>223192.04</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4931,7 +4938,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -4945,7 +4952,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>62</v>
       </c>
@@ -4959,7 +4966,7 @@
         <v>240746.47</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -4973,7 +4980,7 @@
         <v>458922.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4987,7 +4994,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -5001,7 +5008,7 @@
         <v>250778</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -5015,7 +5022,7 @@
         <v>250778.8</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -5029,7 +5036,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -5043,7 +5050,7 @@
         <v>250777.04</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -5057,7 +5064,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -5071,7 +5078,7 @@
         <v>250777</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>62</v>
       </c>
@@ -5085,7 +5092,7 @@
         <v>286649.17</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -5099,7 +5106,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -5113,7 +5120,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -5127,7 +5134,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>62</v>
       </c>
@@ -5141,7 +5148,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -5155,7 +5162,7 @@
         <v>262734.39</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5207,7 +5214,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>57</v>
       </c>
@@ -5221,7 +5228,7 @@
         <v>57532.81</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -5244,7 +5251,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>81</v>
       </c>
@@ -5267,7 +5274,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -5293,7 +5300,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -5313,7 +5320,7 @@
         <v>14994</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -5342,7 +5349,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5371,7 +5378,7 @@
         <v>15047</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -5397,7 +5404,7 @@
         <v>15076</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5443,7 +5450,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5463,7 +5470,7 @@
         <v>15173</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -5515,7 +5522,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5544,7 +5551,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -5596,7 +5603,7 @@
         <v>15606</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>58</v>
       </c>
@@ -5619,7 +5626,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>58</v>
       </c>
@@ -5642,7 +5649,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>58</v>
       </c>
@@ -5665,7 +5672,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>58</v>
       </c>
@@ -5688,7 +5695,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>58</v>
       </c>
@@ -5711,7 +5718,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>58</v>
       </c>
@@ -5760,7 +5767,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5789,7 +5796,7 @@
         <v>15869</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -5838,7 +5845,7 @@
         <v>15927</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5893,7 +5900,7 @@
         <v>16187</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -5919,7 +5926,7 @@
         <v>16012</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5948,7 +5955,7 @@
         <v>16374</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5977,7 +5984,7 @@
         <v>16853</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>57</v>
       </c>
@@ -6003,7 +6010,7 @@
         <v>15710</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>57</v>
       </c>
@@ -6014,7 +6021,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>103</v>
       </c>
@@ -6066,7 +6073,7 @@
         <v>16913</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -6092,7 +6099,7 @@
         <v>16988</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -6121,7 +6128,7 @@
         <v>17132</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>12</v>
       </c>
@@ -6139,6 +6146,9 @@
       </c>
       <c r="F235" s="1">
         <v>46211</v>
+      </c>
+      <c r="G235" s="1">
+        <v>46213</v>
       </c>
       <c r="I235">
         <v>17232</v>
@@ -6170,7 +6180,7 @@
         <v>17230</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>106</v>
       </c>
@@ -6212,11 +6222,14 @@
       <c r="F238" s="1">
         <v>46225</v>
       </c>
+      <c r="G238" s="1">
+        <v>46226</v>
+      </c>
       <c r="I238">
         <v>17378</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>103</v>
       </c>
@@ -6236,8 +6249,57 @@
         <v>46224</v>
       </c>
     </row>
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>5</v>
+      </c>
+      <c r="B240" t="s">
+        <v>107</v>
+      </c>
+      <c r="C240" s="1">
+        <v>46230</v>
+      </c>
+      <c r="D240" s="2">
+        <v>704205.5</v>
+      </c>
+      <c r="E240">
+        <v>1208</v>
+      </c>
+      <c r="F240" s="1">
+        <v>46237</v>
+      </c>
+      <c r="H240" t="s">
+        <v>108</v>
+      </c>
+      <c r="I240">
+        <v>17465</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B241">
+        <v>22</v>
+      </c>
+      <c r="C241" s="1">
+        <v>46237</v>
+      </c>
+      <c r="D241" s="2">
+        <v>50584.959999999999</v>
+      </c>
+      <c r="I241">
+        <v>17543</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A239" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:A241" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="028/2023"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/NOVA_MEDICAO.xlsx
+++ b/NOVA_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F95FDB-4004-4D73-B72A-33F64CE33659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1081E23-8BB6-4C29-A605-8D4F85E661AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AAC94D3E-ED44-400F-9804-ED3D5B3DD77A}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Aditivo" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Aditivo!$A$1:$I$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicoes!$A$1:$A$242</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="109">
   <si>
     <t>007/2024</t>
   </si>
@@ -717,7 +717,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D790DDD-35AF-404B-9777-02841BFD5C41}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I241"/>
+  <dimension ref="A1:I242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -852,7 +852,7 @@
         <v>45582</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -878,7 +878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -904,7 +904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -930,7 +930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -956,7 +956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -982,7 +982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>45750</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>13083</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>45650</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>45848</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>13434</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>13892</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>13968</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>14741</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -5313,6 +5313,15 @@
       <c r="D202" s="2">
         <v>99654.32</v>
       </c>
+      <c r="E202">
+        <v>151</v>
+      </c>
+      <c r="F202" s="1">
+        <v>45999</v>
+      </c>
+      <c r="G202" s="1">
+        <v>46374</v>
+      </c>
       <c r="H202" t="s">
         <v>84</v>
       </c>
@@ -5349,7 +5358,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -5427,7 +5436,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1</v>
       </c>
@@ -5496,7 +5505,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1</v>
       </c>
@@ -5522,7 +5531,7 @@
         <v>15428</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -5577,7 +5586,7 @@
         <v>15490</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1</v>
       </c>
@@ -5741,7 +5750,7 @@
         <v>46048</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1</v>
       </c>
@@ -5767,7 +5776,7 @@
         <v>15798</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5819,7 +5828,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1</v>
       </c>
@@ -5845,7 +5854,7 @@
         <v>15927</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5874,7 +5883,7 @@
         <v>16175</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
@@ -5926,7 +5935,7 @@
         <v>16012</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5955,7 +5964,7 @@
         <v>16374</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -6047,7 +6056,7 @@
         <v>16828</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1</v>
       </c>
@@ -6099,7 +6108,7 @@
         <v>16988</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -6154,7 +6163,7 @@
         <v>17232</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1</v>
       </c>
@@ -6203,7 +6212,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1</v>
       </c>
@@ -6249,7 +6258,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -6267,6 +6276,9 @@
       </c>
       <c r="F240" s="1">
         <v>46237</v>
+      </c>
+      <c r="G240" s="1">
+        <v>46239</v>
       </c>
       <c r="H240" t="s">
         <v>108</v>
@@ -6288,15 +6300,50 @@
       <c r="D241" s="2">
         <v>50584.959999999999</v>
       </c>
+      <c r="E241">
+        <v>353</v>
+      </c>
+      <c r="F241" s="1">
+        <v>46239</v>
+      </c>
+      <c r="G241" s="1">
+        <v>46240</v>
+      </c>
       <c r="I241">
         <v>17543</v>
       </c>
     </row>
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242">
+        <v>23</v>
+      </c>
+      <c r="C242" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D242" s="2">
+        <v>40753.89</v>
+      </c>
+      <c r="E242">
+        <v>354</v>
+      </c>
+      <c r="F242" s="1">
+        <v>46251</v>
+      </c>
+      <c r="G242" s="1">
+        <v>46253</v>
+      </c>
+      <c r="I242">
+        <v>17631</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A241" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:A242" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="028/2023"/>
+        <filter val="009/2022"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6307,7 +6354,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -6892,7 +6939,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -6909,7 +6956,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -6926,7 +6973,7 @@
         <v>45687</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -6937,7 +6984,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -6960,7 +7007,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -6983,7 +7030,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -7508,7 +7555,7 @@
         <v>24.99</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -7531,7 +7578,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -7542,7 +7589,7 @@
         <v>45840</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -7983,7 +8030,7 @@
         <v>46376</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -8075,7 +8122,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -8167,7 +8214,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>0</v>
       </c>
@@ -8190,11 +8237,57 @@
         <v>46472</v>
       </c>
     </row>
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E96" s="1">
+        <v>46219</v>
+      </c>
+      <c r="F96" s="1">
+        <v>46338</v>
+      </c>
+      <c r="G96" s="1">
+        <v>46310</v>
+      </c>
+      <c r="H96" s="1">
+        <v>46429</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" t="s">
+        <v>46</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E97" s="1">
+        <v>46168</v>
+      </c>
+      <c r="F97" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G97" s="1">
+        <v>46234</v>
+      </c>
+      <c r="H97" s="1">
+        <v>46353</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I94" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
+  <autoFilter ref="A1:I96" xr:uid="{C2D9FFEC-3CAE-4AB7-A169-AB095655BC86}">
     <filterColumn colId="0">
       <filters>
-        <filter val="007/2024"/>
+        <filter val="003/2024"/>
       </filters>
     </filterColumn>
   </autoFilter>
